--- a/questionnaire_templates/049_functional_ability_assessment_questionnaire--questionnaire_templates.xlsx
+++ b/questionnaire_templates/049_functional_ability_assessment_questionnaire--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_2.1,_'name':_'independence_level_1',_'label':_'1._independent'}</t>
+          <t>1._independent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 2.1, 'name': 'independence_level_1', 'label': '1. Independent'}</t>
+          <t>1. Independent</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2.2,_'name':_'independence_level_2',_'label':_'2._moderate'}</t>
+          <t>2._moderate</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2.2, 'name': 'independence_level_2', 'label': '2. Moderate'}</t>
+          <t>2. Moderate</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_2.3,_'name':_'independence_level_3',_'label':_'3._needs_assistance'}</t>
+          <t>3._needs_assistance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 2.3, 'name': 'independence_level_3', 'label': '3. Needs Assistance'}</t>
+          <t>3. Needs Assistance</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_3.1,_'name':_'daily_routine_1',_'label':_'1._independent'}</t>
+          <t>1._independent</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 3.1, 'name': 'daily_routine_1', 'label': '1. Independent'}</t>
+          <t>1. Independent</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3.2,_'name':_'daily_routine_2',_'label':_'2._moderate'}</t>
+          <t>2._moderate</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3.2, 'name': 'daily_routine_2', 'label': '2. Moderate'}</t>
+          <t>2. Moderate</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3.3,_'name':_'daily_routine_3',_'label':_'3._needs_assistance'}</t>
+          <t>3._needs_assistance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3.3, 'name': 'daily_routine_3', 'label': '3. Needs Assistance'}</t>
+          <t>3. Needs Assistance</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4.1,_'name':_'bathing_and_dressing_1',_'label':_'1._independent'}</t>
+          <t>1._independent</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4.1, 'name': 'bathing_and_dressing_1', 'label': '1. Independent'}</t>
+          <t>1. Independent</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4.2,_'name':_'bathing_and_dressing_2',_'label':_'2._moderate'}</t>
+          <t>2._moderate</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4.2, 'name': 'bathing_and_dressing_2', 'label': '2. Moderate'}</t>
+          <t>2. Moderate</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4.3,_'name':_'bathing_and_dressing_3',_'label':_'3._needs_assistance'}</t>
+          <t>3._needs_assistance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4.3, 'name': 'bathing_and_dressing_3', 'label': '3. Needs Assistance'}</t>
+          <t>3. Needs Assistance</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5.1,_'name':_'toileting_1',_'label':_'1._independent'}</t>
+          <t>1._independent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5.1, 'name': 'toileting_1', 'label': '1. Independent'}</t>
+          <t>1. Independent</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_5.2,_'name':_'toileting_2',_'label':_'2._moderate'}</t>
+          <t>2._moderate</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 5.2, 'name': 'toileting_2', 'label': '2. Moderate'}</t>
+          <t>2. Moderate</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_5.3,_'name':_'toileting_3',_'label':_'3._needs_assistance'}</t>
+          <t>3._needs_assistance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 5.3, 'name': 'toileting_3', 'label': '3. Needs Assistance'}</t>
+          <t>3. Needs Assistance</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_6.1,_'name':_'feeding_1',_'label':_'1._independent'}</t>
+          <t>1._independent</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 6.1, 'name': 'feeding_1', 'label': '1. Independent'}</t>
+          <t>1. Independent</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_6.2,_'name':_'feeding_2',_'label':_'2._moderate'}</t>
+          <t>2._moderate</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 6.2, 'name': 'feeding_2', 'label': '2. Moderate'}</t>
+          <t>2. Moderate</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_6.3,_'name':_'feeding_3',_'label':_'3._needs_assistance'}</t>
+          <t>3._needs_assistance</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 6.3, 'name': 'feeding_3', 'label': '3. Needs Assistance'}</t>
+          <t>3. Needs Assistance</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_7.1,_'name':_'transfers_1',_'label':_'1._independent'}</t>
+          <t>1._independent</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 7.1, 'name': 'transfers_1', 'label': '1. Independent'}</t>
+          <t>1. Independent</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_7.2,_'name':_'transfers_2',_'label':_'2._moderate'}</t>
+          <t>2._moderate</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 7.2, 'name': 'transfers_2', 'label': '2. Moderate'}</t>
+          <t>2. Moderate</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_7.3,_'name':_'transfers_3',_'label':_'3._needs_assistance'}</t>
+          <t>3._needs_assistance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 7.3, 'name': 'transfers_3', 'label': '3. Needs Assistance'}</t>
+          <t>3. Needs Assistance</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_8.1,_'name':_'mobility_1',_'label':_'1._independent'}</t>
+          <t>1._independent</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 8.1, 'name': 'mobility_1', 'label': '1. Independent'}</t>
+          <t>1. Independent</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_8.2,_'name':_'mobility_2',_'label':_'2._moderate'}</t>
+          <t>2._moderate</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 8.2, 'name': 'mobility_2', 'label': '2. Moderate'}</t>
+          <t>2. Moderate</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_8.3,_'name':_'mobility_3',_'label':_'3._needs_assistance'}</t>
+          <t>3._needs_assistance</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 8.3, 'name': 'mobility_3', 'label': '3. Needs Assistance'}</t>
+          <t>3. Needs Assistance</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_9.1,_'name':_'walking_1',_'label':_'1._independent'}</t>
+          <t>1._independent</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 9.1, 'name': 'walking_1', 'label': '1. Independent'}</t>
+          <t>1. Independent</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_9.2,_'name':_'walking_2',_'label':_'2._moderate'}</t>
+          <t>2._moderate</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 9.2, 'name': 'walking_2', 'label': '2. Moderate'}</t>
+          <t>2. Moderate</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_9.3,_'name':_'walking_3',_'label':_'3._needs_assistance'}</t>
+          <t>3._needs_assistance</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 9.3, 'name': 'walking_3', 'label': '3. Needs Assistance'}</t>
+          <t>3. Needs Assistance</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_10.1,_'name':_'communication_1',_'label':_'1._independent'}</t>
+          <t>1._independent</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 10.1, 'name': 'communication_1', 'label': '1. Independent'}</t>
+          <t>1. Independent</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_10.2,_'name':_'communication_2',_'label':_'2._moderate'}</t>
+          <t>2._moderate</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 10.2, 'name': 'communication_2', 'label': '2. Moderate'}</t>
+          <t>2. Moderate</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_10.3,_'name':_'communication_3',_'label':_'3._needs_assistance'}</t>
+          <t>3._needs_assistance</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 10.3, 'name': 'communication_3', 'label': '3. Needs Assistance'}</t>
+          <t>3. Needs Assistance</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_11.1,_'name':_'social_interaction_1',_'label':_'1._independent'}</t>
+          <t>1._independent</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 11.1, 'name': 'social_interaction_1', 'label': '1. Independent'}</t>
+          <t>1. Independent</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_11.2,_'name':_'social_interaction_2',_'label':_'2._moderate'}</t>
+          <t>2._moderate</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 11.2, 'name': 'social_interaction_2', 'label': '2. Moderate'}</t>
+          <t>2. Moderate</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_11.3,_'name':_'social_interaction_3',_'label':_'3._needs_assistance'}</t>
+          <t>3._needs_assistance</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 11.3, 'name': 'social_interaction_3', 'label': '3. Needs Assistance'}</t>
+          <t>3. Needs Assistance</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_12.1,_'name':_'sleep_1',_'label':_'1._independent'}</t>
+          <t>1._independent</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 12.1, 'name': 'sleep_1', 'label': '1. Independent'}</t>
+          <t>1. Independent</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_12.2,_'name':_'sleep_2',_'label':_'2._moderate'}</t>
+          <t>2._moderate</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 12.2, 'name': 'sleep_2', 'label': '2. Moderate'}</t>
+          <t>2. Moderate</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_12.3,_'name':_'sleep_3',_'label':_'3._needs_assistance'}</t>
+          <t>3._needs_assistance</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 12.3, 'name': 'sleep_3', 'label': '3. Needs Assistance'}</t>
+          <t>3. Needs Assistance</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_13.1,_'name':_'leisure_activities_1',_'label':_'1._independent'}</t>
+          <t>1._independent</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 13.1, 'name': 'leisure_activities_1', 'label': '1. Independent'}</t>
+          <t>1. Independent</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_13.2,_'name':_'leisure_activities_2',_'label':_'2._moderate'}</t>
+          <t>2._moderate</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 13.2, 'name': 'leisure_activities_2', 'label': '2. Moderate'}</t>
+          <t>2. Moderate</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_13.3,_'name':_'leisure_activities_3',_'label':_'3._needs_assistance'}</t>
+          <t>3._needs_assistance</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 13.3, 'name': 'leisure_activities_3', 'label': '3. Needs Assistance'}</t>
+          <t>3. Needs Assistance</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_14.1,_'name':_'personal_care_1',_'label':_'1._independent'}</t>
+          <t>1._independent</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 14.1, 'name': 'personal_care_1', 'label': '1. Independent'}</t>
+          <t>1. Independent</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_14.2,_'name':_'personal_care_2',_'label':_'2._moderate'}</t>
+          <t>2._moderate</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 14.2, 'name': 'personal_care_2', 'label': '2. Moderate'}</t>
+          <t>2. Moderate</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_'14.2.1',_'name':_'personal_care_2.1',_'label':_2.1}</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': '14.2.1', 'name': 'personal_care_2.1', 'label': 2.1}</t>
+          <t>2.1</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_14.3,_'name':_'personal_care_3',_'label':_'3._needs_assistance'}</t>
+          <t>3._needs_assistance</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 14.3, 'name': 'personal_care_3', 'label': '3. Needs Assistance'}</t>
+          <t>3. Needs Assistance</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_15.1,_'name':_'continence_1',_'label':_'1._independent'}</t>
+          <t>1._independent</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 15.1, 'name': 'continence_1', 'label': '1. Independent'}</t>
+          <t>1. Independent</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_15.2,_'name':_'continence_2',_'label':_'2._moderate'}</t>
+          <t>2._moderate</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 15.2, 'name': 'continence_2', 'label': '2. Moderate'}</t>
+          <t>2. Moderate</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_15.3,_'name':_'continence_3',_'label':_'3._needs_assistance'}</t>
+          <t>3._needs_assistance</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 15.3, 'name': 'continence_3', 'label': '3. Needs Assistance'}</t>
+          <t>3. Needs Assistance</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_16.1,_'name':_'medication_1',_'label':_'1._independent'}</t>
+          <t>1._independent</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 16.1, 'name': 'medication_1', 'label': '1. Independent'}</t>
+          <t>1. Independent</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_16.2,_'name':_'medication_2',_'label':_'2._moderate'}</t>
+          <t>2._moderate</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 16.2, 'name': 'medication_2', 'label': '2. Moderate'}</t>
+          <t>2. Moderate</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_'16.2.1',_'name':_'medication_2.1',_'label':_2.1}</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': '16.2.1', 'name': 'medication_2.1', 'label': 2.1}</t>
+          <t>2.1</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_16.3,_'name':_'medication_3',_'label':_'3._needs_assistance'}</t>
+          <t>3._needs_assistance</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 16.3, 'name': 'medication_3', 'label': '3. Needs Assistance'}</t>
+          <t>3. Needs Assistance</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_17.1,_'name':_'medical_conditions_1',_'label':_'1._independent'}</t>
+          <t>1._independent</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 17.1, 'name': 'medical_conditions_1', 'label': '1. Independent'}</t>
+          <t>1. Independent</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_17.2,_'name':_'medical_conditions_2',_'label':_'2._moderate'}</t>
+          <t>2._moderate</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 17.2, 'name': 'medical_conditions_2', 'label': '2. Moderate'}</t>
+          <t>2. Moderate</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_17.3,_'name':_'medical_conditions_3',_'label':_'3._needs_assistance'}</t>
+          <t>3._needs_assistance</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 17.3, 'name': 'medical_conditions_3', 'label': '3. Needs Assistance'}</t>
+          <t>3. Needs Assistance</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_18.1,_'name':_'mental_health_1',_'label':_'1._independent'}</t>
+          <t>1._independent</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 18.1, 'name': 'mental_health_1', 'label': '1. Independent'}</t>
+          <t>1. Independent</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_18.2,_'name':_'mental_health_2',_'label':_'2._moderate'}</t>
+          <t>2._moderate</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 18.2, 'name': 'mental_health_2', 'label': '2. Moderate'}</t>
+          <t>2. Moderate</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_18.3,_'name':_'mental_health_3',_'label':_'3._needs_assistance'}</t>
+          <t>3._needs_assistance</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 18.3, 'name': 'mental_health_3', 'label': '3. Needs Assistance'}</t>
+          <t>3. Needs Assistance</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_19.1,_'name':_'safety_1',_'label':_'1._independent'}</t>
+          <t>1._independent</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': 19.1, 'name': 'safety_1', 'label': '1. Independent'}</t>
+          <t>1. Independent</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'id':_19.2,_'name':_'safety_2',_'label':_'2._moderate'}</t>
+          <t>2._moderate</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'id': 19.2, 'name': 'safety_2', 'label': '2. Moderate'}</t>
+          <t>2. Moderate</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'id':_19.3,_'name':_'safety_3',_'label':_'3._needs_assistance'}</t>
+          <t>3._needs_assistance</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'id': 19.3, 'name': 'safety_3', 'label': '3. Needs Assistance'}</t>
+          <t>3. Needs Assistance</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'id':_20.1,_'name':_'medical_history_1',_'label':_'1._independent'}</t>
+          <t>1._independent</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'id': 20.1, 'name': 'medical_history_1', 'label': '1. Independent'}</t>
+          <t>1. Independent</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'id':_20.2,_'name':_'medical_history_2',_'label':_'2._moderate'}</t>
+          <t>2._moderate</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'id': 20.2, 'name': 'medical_history_2', 'label': '2. Moderate'}</t>
+          <t>2. Moderate</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'id':_20.3,_'name':_'medical_history_3',_'label':_'3._needs_assistance'}</t>
+          <t>3._needs_assistance</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'id': 20.3, 'name': 'medical_history_3', 'label': '3. Needs Assistance'}</t>
+          <t>3. Needs Assistance</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'id':_21.1,_'name':_'cognitive_1',_'label':_'1._independent'}</t>
+          <t>1._independent</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'id': 21.1, 'name': 'cognitive_1', 'label': '1. Independent'}</t>
+          <t>1. Independent</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'id':_21.2,_'name':_'cognitive_2',_'label':_'2._moderate'}</t>
+          <t>2._moderate</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'id': 21.2, 'name': 'cognitive_2', 'label': '2. Moderate'}</t>
+          <t>2. Moderate</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'id':_21.3,_'name':_'cognitive_3',_'label':_'3._needs_assistance'}</t>
+          <t>3._needs_assistance</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'id': 21.3, 'name': 'cognitive_3', 'label': '3. Needs Assistance'}</t>
+          <t>3. Needs Assistance</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'id':_22.1,_'name':_'social_services_1',_'label':_'1._independent'}</t>
+          <t>1._independent</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'id': 22.1, 'name': 'social_services_1', 'label': '1. Independent'}</t>
+          <t>1. Independent</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'id':_22.2,_'name':_'social_services_2',_'label':_'2._moderate'}</t>
+          <t>2._moderate</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'id': 22.2, 'name': 'social_services_2', 'label': '2. Moderate'}</t>
+          <t>2. Moderate</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'id':_22.3,_'name':_'social_services_3',_'label':_'3._needs_assistance'}</t>
+          <t>3._needs_assistance</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'id': 22.3, 'name': 'social_services_3', 'label': '3. Needs Assistance'}</t>
+          <t>3. Needs Assistance</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'id':_23.1,_'name':_'home_safety_1',_'label':_'1._independent'}</t>
+          <t>1._independent</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'id': 23.1, 'name': 'home_safety_1', 'label': '1. Independent'}</t>
+          <t>1. Independent</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'id':_23.2,_'name':_'home_safety_2',_'label':_'2._moderate'}</t>
+          <t>2._moderate</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'id': 23.2, 'name': 'home_safety_2', 'label': '2. Moderate'}</t>
+          <t>2. Moderate</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'id':_23.3,_'name':_'home_safety_3',_'label':_'3._needs_assistance'}</t>
+          <t>3._needs_assistance</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'id': 23.3, 'name': 'home_safety_3', 'label': '3. Needs Assistance'}</t>
+          <t>3. Needs Assistance</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'id':_24.1,_'name':_'financial_1',_'label':_'1._independent'}</t>
+          <t>1._independent</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'id': 24.1, 'name': 'financial_1', 'label': '1. Independent'}</t>
+          <t>1. Independent</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'id':_24.2,_'name':_'financial_2',_'label':_'2._moderate'}</t>
+          <t>2._moderate</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'id': 24.2, 'name': 'financial_2', 'label': '2. Moderate'}</t>
+          <t>2. Moderate</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'id':_24.3,_'name':_'financial_3',_'label':_'3._needs_assistance'}</t>
+          <t>3._needs_assistance</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'id': 24.3, 'name': 'financial_3', 'label': '3. Needs Assistance'}</t>
+          <t>3. Needs Assistance</t>
         </is>
       </c>
     </row>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'id':_25.1,_'name':_'other_needs_1',_'label':_'1._independent'}</t>
+          <t>1._independent</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'id': 25.1, 'name': 'other_needs_1', 'label': '1. Independent'}</t>
+          <t>1. Independent</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'id':_25.2,_'name':_'other_needs_2',_'label':_'2._moderate'}</t>
+          <t>2._moderate</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'id': 25.2, 'name': 'other_needs_2', 'label': '2. Moderate'}</t>
+          <t>2. Moderate</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'id':_25.3,_'name':_'other_needs_3',_'label':_'3._needs_assistance'}</t>
+          <t>3._needs_assistance</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'id': 25.3, 'name': 'other_needs_3', 'label': '3. Needs Assistance'}</t>
+          <t>3. Needs Assistance</t>
         </is>
       </c>
     </row>
